--- a/90606_REPORT_BOTTEGA_04-01-2026.xlsx
+++ b/90606_REPORT_BOTTEGA_04-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="99">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 04/01/2026</t>
   </si>
   <si>
@@ -73,16 +107,70 @@
     <t>% TOT</t>
   </si>
   <si>
+    <t>610003</t>
+  </si>
+  <si>
+    <t>Bistecca Costata 30-40 G</t>
+  </si>
+  <si>
+    <t>50-004-011-002070</t>
+  </si>
+  <si>
+    <t>Hamburger bovino adulto (con patate)</t>
+  </si>
+  <si>
+    <t>50-004-011-000860</t>
+  </si>
+  <si>
+    <t>Patate Al Forno</t>
+  </si>
+  <si>
+    <t>610007</t>
+  </si>
+  <si>
+    <t>Bistecca Con Filetto 30-40 G</t>
+  </si>
+  <si>
+    <t>50-004-011-000600</t>
+  </si>
+  <si>
+    <t>Grigliata Mista</t>
+  </si>
+  <si>
+    <t>50-004-011-002120</t>
+  </si>
+  <si>
+    <t>Controfiletto B.A.</t>
+  </si>
+  <si>
     <t>610005</t>
   </si>
   <si>
     <t xml:space="preserve">Bistecca Con Filetto </t>
   </si>
   <si>
-    <t>50-004-011-002070</t>
-  </si>
-  <si>
-    <t>Hamburger bovino adulto (con patate)</t>
+    <t>50-004-011-000610</t>
+  </si>
+  <si>
+    <t>Grigliata Mista Xxl</t>
+  </si>
+  <si>
+    <t>50-004-011-000750</t>
+  </si>
+  <si>
+    <t>Punta Di Petto (Con Patate)</t>
+  </si>
+  <si>
+    <t>50-004-011-001300</t>
+  </si>
+  <si>
+    <t>Costine di suino</t>
+  </si>
+  <si>
+    <t>50-004-011-000590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filetto B.A. </t>
   </si>
   <si>
     <t>50-004-011-002160</t>
@@ -91,40 +179,10 @@
     <t>Pancetta Porchettata (Con Patate)</t>
   </si>
   <si>
-    <t>50-004-011-002120</t>
-  </si>
-  <si>
-    <t>Controfiletto B.A.</t>
-  </si>
-  <si>
-    <t>50-004-011-000750</t>
-  </si>
-  <si>
-    <t>Punta Di Petto (Con Patate)</t>
-  </si>
-  <si>
-    <t>50-004-011-000860</t>
-  </si>
-  <si>
-    <t>Patate Al Forno</t>
-  </si>
-  <si>
-    <t>50-004-011-001300</t>
-  </si>
-  <si>
-    <t>Costine di suino</t>
-  </si>
-  <si>
-    <t>50-004-011-000600</t>
-  </si>
-  <si>
-    <t>Grigliata Mista</t>
-  </si>
-  <si>
-    <t>50-004-011-000590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filetto B.A. </t>
+    <t>50-004-011-001680</t>
+  </si>
+  <si>
+    <t>Verdure</t>
   </si>
   <si>
     <t>610001</t>
@@ -133,16 +191,10 @@
     <t>Bistecca In Costata</t>
   </si>
   <si>
-    <t>50-004-011-000610</t>
-  </si>
-  <si>
-    <t>Grigliata Mista Xxl</t>
-  </si>
-  <si>
-    <t>50-004-011-001680</t>
-  </si>
-  <si>
-    <t>Verdure</t>
+    <t>50-004-011-000700</t>
+  </si>
+  <si>
+    <t>Tagliata Pollo</t>
   </si>
   <si>
     <t>50-004-011-002230</t>
@@ -151,48 +203,48 @@
     <t>Pollo Alla Cacciatora Con Contorno</t>
   </si>
   <si>
+    <t>50-004-011-000670</t>
+  </si>
+  <si>
+    <t>Spiedini Misti</t>
+  </si>
+  <si>
+    <t>610008</t>
+  </si>
+  <si>
+    <t>Bistecca Con Filetto 40-60 G</t>
+  </si>
+  <si>
+    <t>50-004-011-000650</t>
+  </si>
+  <si>
+    <t>Mezzo Pollo Ruspante</t>
+  </si>
+  <si>
     <t>50-004-011-000710</t>
   </si>
   <si>
     <t>Etrusca Marinata Birra (Con Patate)</t>
   </si>
   <si>
-    <t>50-004-011-000700</t>
-  </si>
-  <si>
-    <t>Tagliata Pollo</t>
-  </si>
-  <si>
-    <t>50-004-011-000650</t>
-  </si>
-  <si>
-    <t>Mezzo Pollo Ruspante</t>
-  </si>
-  <si>
-    <t>50-004-011-000670</t>
-  </si>
-  <si>
-    <t>Spiedini Misti</t>
-  </si>
-  <si>
     <t>50-004-011-002080</t>
   </si>
   <si>
     <t>Hamburger suino (con patate)</t>
   </si>
   <si>
+    <t>50-004-011-002220</t>
+  </si>
+  <si>
+    <t>Pollo Allo Spiedo</t>
+  </si>
+  <si>
     <t>610041</t>
   </si>
   <si>
     <t>Costata (Asporto)</t>
   </si>
   <si>
-    <t>50-004-011-002220</t>
-  </si>
-  <si>
-    <t>Pollo Allo Spiedo</t>
-  </si>
-  <si>
     <t>50-004-011-002280</t>
   </si>
   <si>
@@ -245,6 +297,21 @@
   </si>
   <si>
     <t>12:00-15:59</t>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>04/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>28/12/2025</t>
   </si>
 </sst>
 </file>
@@ -382,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -395,13 +462,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -489,27 +570,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>4019.0</v>
+      <c r="B11" t="n" s="5">
+        <v>279.8181</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>4015.68</v>
+      <c r="B12" t="n" s="7">
+        <v>168.6363</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>0.08</v>
+      <c r="B13" t="n" s="5">
+        <v>648.5456</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>1398.4999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>392.6365</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>99.2727</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>7006.41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>7417.14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>-5.54</v>
       </c>
     </row>
   </sheetData>
@@ -519,7 +688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -531,458 +700,458 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>451.2272</v>
+        <v>740.7727</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>8.27</v>
+        <v>15.2</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>11.23</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>353.8182</v>
+        <v>556.0</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>28.0</v>
+        <v>44.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>8.8</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>327.2727</v>
+        <v>539.4546</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>20.0</v>
+        <v>99.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>8.14</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>320.7272</v>
+        <v>504.9999</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>17.0</v>
+        <v>8.68</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>7.98</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>309.1818</v>
+        <v>487.6363</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>19.0</v>
+        <v>30.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>7.69</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>300.0</v>
+        <v>469.6181</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>55.0</v>
+        <v>25.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>7.46</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>295.2728</v>
+        <v>451.2272</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>22.0</v>
+        <v>8.27</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>7.35</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>291.2727</v>
+        <v>441.8183</v>
       </c>
       <c r="D9" t="n" s="5">
         <v>18.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>7.25</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>230.0</v>
+        <v>390.5454</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>11.0</v>
+        <v>24.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>5.72</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>198.6363</v>
+        <v>387.3728</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>4.37</v>
+        <v>29.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>4.94</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>196.3637</v>
+        <v>355.4546</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>4.89</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>150.1819</v>
+        <v>327.2727</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>3.74</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>88.4547</v>
+        <v>252.0001</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>7.0</v>
+        <v>40.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>81.8182</v>
+        <v>198.6363</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>5.0</v>
+        <v>4.37</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>2.04</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>70.3636</v>
+        <v>114.9181</v>
       </c>
       <c r="D16" t="n" s="7">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>59.4546</v>
+        <v>113.7275</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>50.5456</v>
+        <v>113.7274</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>50.5454</v>
+        <v>96.0</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>4.0</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>43.5909</v>
+        <v>89.1819</v>
       </c>
       <c r="D20" t="n" s="7">
-        <v>1.3</v>
+        <v>9.0</v>
       </c>
       <c r="E20" t="n" s="7">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" t="n" s="5">
-        <v>38.1818</v>
+        <v>81.8182</v>
       </c>
       <c r="D21" t="n" s="5">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E21" t="n" s="5">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n" s="7">
-        <v>36.0</v>
+        <v>75.8182</v>
       </c>
       <c r="D22" t="n" s="7">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E22" t="n" s="7">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n" s="5">
-        <v>16.3636</v>
+        <v>57.2727</v>
       </c>
       <c r="D23" t="n" s="5">
         <v>3.0</v>
       </c>
       <c r="E23" t="n" s="5">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C24" t="n" s="7">
-        <v>16.3635</v>
+        <v>43.5909</v>
       </c>
       <c r="D24" t="n" s="7">
-        <v>3.0</v>
+        <v>1.3</v>
       </c>
       <c r="E24" t="n" s="7">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C25" t="n" s="5">
-        <v>13.9636</v>
+        <v>36.0</v>
       </c>
       <c r="D25" t="n" s="5">
-        <v>0.67</v>
+        <v>4.0</v>
       </c>
       <c r="E25" t="n" s="5">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n" s="7">
-        <v>13.6364</v>
+        <v>21.8181</v>
       </c>
       <c r="D26" t="n" s="7">
-        <v>0.25</v>
+        <v>4.0</v>
       </c>
       <c r="E26" t="n" s="7">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C27" t="n" s="5">
-        <v>9.4</v>
+        <v>16.3635</v>
       </c>
       <c r="D27" t="n" s="5">
-        <v>0.53</v>
+        <v>3.0</v>
       </c>
       <c r="E27" t="n" s="5">
         <v>0.23</v>
@@ -990,33 +1159,84 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C28" t="n" s="7">
+        <v>13.9636</v>
+      </c>
+      <c r="D28" t="n" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="E28" t="n" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C29" t="n" s="5">
+        <v>13.6364</v>
+      </c>
+      <c r="D29" t="n" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="E29" t="n" s="5">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C30" t="n" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="D30" t="n" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="E30" t="n" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C31" t="n" s="5">
         <v>6.3636</v>
       </c>
-      <c r="D28" t="n" s="7">
+      <c r="D31" t="n" s="5">
         <v>1.0</v>
       </c>
-      <c r="E28" t="n" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" t="n" s="1">
-        <v>4019.0</v>
-      </c>
-      <c r="D29" t="n" s="1">
-        <v>282.39</v>
-      </c>
-      <c r="E29" t="n" s="1">
+      <c r="E31" t="n" s="5">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" t="n" s="1">
+        <v>7006.41</v>
+      </c>
+      <c r="D32" t="n" s="1">
+        <v>449.87</v>
+      </c>
+      <c r="E32" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -1027,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -1038,13 +1258,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1052,15 +1272,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>4.0</v>
@@ -1071,10 +1291,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>3.0</v>
@@ -1085,10 +1305,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>2.0</v>
@@ -1099,10 +1319,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>2.0</v>
@@ -1113,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>1.93</v>
@@ -1127,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>1.0</v>
@@ -1141,10 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>1.0</v>
@@ -1155,10 +1375,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>1.0</v>
@@ -1169,10 +1389,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>1.0</v>
@@ -1183,10 +1403,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>1.0</v>
@@ -1197,10 +1417,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>1.0</v>
@@ -1211,10 +1431,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>1.0</v>
@@ -1225,10 +1445,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>1.0</v>
@@ -1239,10 +1459,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>1.0</v>
@@ -1253,10 +1473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C17" t="n" s="1">
         <v>21.93</v>
@@ -1268,15 +1488,15 @@
     <row r="18"/>
     <row r="19">
       <c r="A19" t="s" s="1">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>52.0</v>
@@ -1287,10 +1507,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>28.0</v>
@@ -1301,10 +1521,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>22.0</v>
@@ -1315,10 +1535,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>21.0</v>
@@ -1329,10 +1549,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>18.0</v>
@@ -1343,10 +1563,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>17.0</v>
@@ -1357,10 +1577,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>16.0</v>
@@ -1371,10 +1591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>15.0</v>
@@ -1385,10 +1605,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>10.0</v>
@@ -1399,10 +1619,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>8.0</v>
@@ -1413,10 +1633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>6.34</v>
@@ -1427,10 +1647,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C31" t="n" s="5">
         <v>6.0</v>
@@ -1441,10 +1661,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C32" t="n" s="7">
         <v>6.0</v>
@@ -1455,10 +1675,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C33" t="n" s="5">
         <v>5.0</v>
@@ -1469,10 +1689,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C34" t="n" s="7">
         <v>5.0</v>
@@ -1483,10 +1703,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C35" t="n" s="5">
         <v>4.37</v>
@@ -1497,10 +1717,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="4">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s" s="4">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C36" t="n" s="7">
         <v>4.0</v>
@@ -1511,10 +1731,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C37" t="n" s="5">
         <v>3.0</v>
@@ -1525,10 +1745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="4">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s" s="4">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C38" t="n" s="7">
         <v>3.0</v>
@@ -1539,10 +1759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C39" t="n" s="5">
         <v>3.0</v>
@@ -1553,10 +1773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="4">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s" s="4">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C40" t="n" s="7">
         <v>2.0</v>
@@ -1567,10 +1787,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C41" t="n" s="5">
         <v>2.0</v>
@@ -1581,10 +1801,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="4">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s" s="4">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C42" t="n" s="7">
         <v>1.3</v>
@@ -1595,10 +1815,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C43" t="n" s="5">
         <v>1.0</v>
@@ -1609,10 +1829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="4">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s" s="4">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C44" t="n" s="7">
         <v>0.67</v>
@@ -1623,10 +1843,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C45" t="n" s="5">
         <v>0.53</v>
@@ -1637,10 +1857,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="4">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s" s="4">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C46" t="n" s="7">
         <v>0.25</v>
@@ -1651,10 +1871,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="1">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C47" t="n" s="1">
         <v>260.46</v>
@@ -1664,13 +1884,585 @@
       </c>
     </row>
     <row r="48"/>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="C50" t="n" s="7">
+        <v>14.0</v>
+      </c>
+      <c r="D50" t="n" s="7">
+        <v>76.3637</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C51" t="n" s="5">
+        <v>6.4</v>
+      </c>
+      <c r="D51" t="n" s="5">
+        <v>314.1818</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="B52" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="C52" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D52" t="n" s="7">
+        <v>65.0091</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C53" t="n" s="5">
+        <v>4.48</v>
+      </c>
+      <c r="D53" t="n" s="5">
+        <v>260.6363</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C54" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D54" t="n" s="7">
+        <v>65.4545</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C55" t="n" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D55" t="n" s="5">
+        <v>65.0909</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="B56" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="C56" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D56" t="n" s="7">
+        <v>50.5454</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C57" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D57" t="n" s="5">
+        <v>53.4364</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="4">
+        <v>54</v>
+      </c>
+      <c r="B58" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="C58" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D58" t="n" s="7">
+        <v>19.0909</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C59" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D59" t="n" s="5">
+        <v>24.5455</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="B60" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="C60" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D60" t="n" s="7">
+        <v>20.9091</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C61" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D61" t="n" s="5">
+        <v>19.0909</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C62" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D62" t="n" s="7">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C63" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D63" t="n" s="5">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="B64" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="C64" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D64" t="n" s="7">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C65" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D65" t="n" s="5">
+        <v>9.9091</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="B66" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="C66" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D66" t="n" s="7">
+        <v>9.3727</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C67" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D67" t="n" s="5">
+        <v>5.4545</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="B68" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="C68" t="n" s="1">
+        <v>56.88</v>
+      </c>
+      <c r="D68" t="n" s="1">
+        <v>1097.0</v>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C71" t="n" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="D71" t="n" s="5">
+        <v>163.0909</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="4">
+        <v>54</v>
+      </c>
+      <c r="B72" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="C72" t="n" s="7">
+        <v>13.0</v>
+      </c>
+      <c r="D72" t="n" s="7">
+        <v>82.7273</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C73" t="n" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="D73" t="n" s="5">
+        <v>151.6364</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="4">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s" s="4">
+        <v>45</v>
+      </c>
+      <c r="C74" t="n" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="D74" t="n" s="7">
+        <v>220.9091</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C75" t="n" s="5">
+        <v>8.8</v>
+      </c>
+      <c r="D75" t="n" s="5">
+        <v>426.5909</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C76" t="n" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="D76" t="n" s="7">
+        <v>130.9091</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C77" t="n" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="D77" t="n" s="5">
+        <v>104.5455</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B78" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C78" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D78" t="n" s="7">
+        <v>95.4545</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C79" t="n" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="D79" t="n" s="5">
+        <v>244.3636</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B80" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C80" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D80" t="n" s="7">
+        <v>50.5454</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C81" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D81" t="n" s="5">
+        <v>35.1818</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="B82" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="C82" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D82" t="n" s="7">
+        <v>27.0909</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C83" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D83" t="n" s="5">
+        <v>19.8182</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="B84" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="C84" t="n" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="D84" t="n" s="7">
+        <v>96.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C85" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D85" t="n" s="5">
+        <v>16.2727</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="4">
+        <v>70</v>
+      </c>
+      <c r="B86" t="s" s="4">
+        <v>71</v>
+      </c>
+      <c r="C86" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D86" t="n" s="7">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C87" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D87" t="n" s="5">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="B88" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="C88" t="n" s="1">
+        <v>110.6</v>
+      </c>
+      <c r="D88" t="n" s="1">
+        <v>1890.41</v>
+      </c>
+    </row>
+    <row r="89"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A88:B88"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>